--- a/translation_tbl/CRS610_PYCD.xlsx
+++ b/translation_tbl/CRS610_PYCD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\w10itasv\Documents\DevDataMigration\DevDataMigrationTool\GitHubDataMigration\DataMigrationTool\translation_tbl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7D9FA0D-8E61-4203-8D50-1472C8B59D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED6560C-ECC2-422C-886C-DDB4F259542C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="420" yWindow="2085" windowWidth="17280" windowHeight="8880" xr2:uid="{3F205CE4-4708-49C9-B756-F5FE710B0EA1}"/>
+    <workbookView xWindow="7770" yWindow="4020" windowWidth="17280" windowHeight="8880" xr2:uid="{3F205CE4-4708-49C9-B756-F5FE710B0EA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>CH1</t>
   </si>
@@ -60,6 +60,12 @@
   </si>
   <si>
     <t>NEW</t>
+  </si>
+  <si>
+    <t>060</t>
+  </si>
+  <si>
+    <t>010</t>
   </si>
 </sst>
 </file>
@@ -108,16 +114,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,75 +461,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C851F6D6-45F1-4898-AC0F-4B5A5C280C51}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="6"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>10</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <v>20</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <v>30</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <v>40</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <v>50</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>60</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
